--- a/mlb_weather_professional_v5_2026_07_28.xlsx
+++ b/mlb_weather_professional_v5_2026_07_28.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="410">
   <si>
     <t>Date</t>
   </si>
@@ -623,52 +623,46 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-07-27 11:10:29 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:30 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:31 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:32 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:33 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:34 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:35 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:36 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:38 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:40 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:42 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:43 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:45 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:46 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:48 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-27 11:10:49 PM PDT</t>
+    <t>2026-07-27 11:11:39 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:40 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:41 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:42 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:43 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:44 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:46 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:47 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:48 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:50 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:51 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:52 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:53 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-27 11:11:54 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -1058,52 +1052,46 @@
     <t>10:10 PM PDT</t>
   </si>
   <si>
-    <t>2026-07-28 06:10:29 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:30 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:31 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:32 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:33 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:34 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:35 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:36 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:38 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:40 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:42 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:43 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:45 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:46 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:48 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-28 06:10:49 UTC</t>
+    <t>2026-07-28 06:11:39 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:40 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:41 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:42 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:43 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:44 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:46 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:47 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:48 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:50 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:51 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:52 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:53 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-28 06:11:54 UTC</t>
   </si>
   <si>
     <t>2026-07-28T05:48:49+00:00</t>
@@ -2072,7 +2060,7 @@
         <v>200</v>
       </c>
       <c r="AZ2">
-        <v>21.7</v>
+        <v>22.8</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -2230,7 +2218,7 @@
         <v>201</v>
       </c>
       <c r="AZ3">
-        <v>140.9</v>
+        <v>142</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2364,7 +2352,7 @@
         <v>191</v>
       </c>
       <c r="AR4">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -2388,7 +2376,7 @@
         <v>202</v>
       </c>
       <c r="AZ4">
-        <v>144</v>
+        <v>145.1</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2546,7 +2534,7 @@
         <v>203</v>
       </c>
       <c r="AZ5">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2680,7 +2668,7 @@
         <v>192</v>
       </c>
       <c r="AR6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AS6">
         <v>0</v>
@@ -2704,7 +2692,7 @@
         <v>204</v>
       </c>
       <c r="AZ6">
-        <v>578.9</v>
+        <v>580.1</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2838,7 +2826,7 @@
         <v>193</v>
       </c>
       <c r="AR7">
-        <v>-2.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AS7">
         <v>0</v>
@@ -2862,7 +2850,7 @@
         <v>205</v>
       </c>
       <c r="AZ7">
-        <v>197.5</v>
+        <v>198.7</v>
       </c>
       <c r="BA7">
         <v>5</v>
@@ -2996,7 +2984,7 @@
         <v>190</v>
       </c>
       <c r="AR8">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AS8">
         <v>0</v>
@@ -3017,10 +3005,10 @@
         <v>8.1</v>
       </c>
       <c r="AY8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AZ8">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3154,7 +3142,7 @@
         <v>190</v>
       </c>
       <c r="AR9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS9">
         <v>0</v>
@@ -3175,10 +3163,10 @@
         <v>21.4</v>
       </c>
       <c r="AY9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AZ9">
-        <v>679</v>
+        <v>680.1</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3312,7 +3300,7 @@
         <v>194</v>
       </c>
       <c r="AR10">
-        <v>-4.6</v>
+        <v>-4.1</v>
       </c>
       <c r="AS10">
         <v>0</v>
@@ -3333,10 +3321,10 @@
         <v>9.1</v>
       </c>
       <c r="AY10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AZ10">
-        <v>34.1</v>
+        <v>35.3</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3470,7 +3458,7 @@
         <v>190</v>
       </c>
       <c r="AR11">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AS11">
         <v>0</v>
@@ -3491,10 +3479,10 @@
         <v>16.4</v>
       </c>
       <c r="AY11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AZ11">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3628,7 +3616,7 @@
         <v>194</v>
       </c>
       <c r="AR12">
-        <v>-8.699999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="AS12">
         <v>0</v>
@@ -3649,10 +3637,10 @@
         <v>7.5</v>
       </c>
       <c r="AY12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AZ12">
-        <v>79</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3786,7 +3774,7 @@
         <v>190</v>
       </c>
       <c r="AR13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS13">
         <v>0</v>
@@ -3807,10 +3795,10 @@
         <v>13</v>
       </c>
       <c r="AY13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AZ13">
-        <v>618.1</v>
+        <v>619.3</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3965,10 +3953,10 @@
         <v>6.3</v>
       </c>
       <c r="AY14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AZ14">
-        <v>549.7</v>
+        <v>550.8</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -4102,7 +4090,7 @@
         <v>192</v>
       </c>
       <c r="AR15">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="AS15">
         <v>0</v>
@@ -4123,10 +4111,10 @@
         <v>10.8</v>
       </c>
       <c r="AY15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AZ15">
-        <v>618.2</v>
+        <v>619.3</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4281,10 +4269,10 @@
         <v>13</v>
       </c>
       <c r="AY16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AZ16">
-        <v>163.9</v>
+        <v>165</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4418,7 +4406,7 @@
         <v>191</v>
       </c>
       <c r="AR17">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AS17">
         <v>0</v>
@@ -4439,10 +4427,10 @@
         <v>12.3</v>
       </c>
       <c r="AY17" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AZ17">
-        <v>148.8</v>
+        <v>149.8</v>
       </c>
       <c r="BA17">
         <v>5</v>
@@ -4582,286 +4570,286 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="CU1" s="1" t="s">
         <v>49</v>
@@ -4870,16 +4858,16 @@
         <v>48</v>
       </c>
       <c r="CW1" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="CY1" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:104">
@@ -4896,22 +4884,22 @@
         <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H2" t="s">
         <v>200</v>
       </c>
       <c r="I2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J2">
-        <v>21.7</v>
+        <v>22.8</v>
       </c>
       <c r="K2">
         <v>11.5</v>
@@ -4941,13 +4929,13 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="V2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="W2">
         <v>0.6667</v>
@@ -5037,10 +5025,10 @@
         <v>339.5</v>
       </c>
       <c r="AZ2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB2">
         <v>87</v>
@@ -5127,7 +5115,7 @@
         <v>1.1198</v>
       </c>
       <c r="CD2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE2">
         <v>2738</v>
@@ -5210,22 +5198,22 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H3" t="s">
         <v>200</v>
       </c>
       <c r="I3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J3">
-        <v>21.7</v>
+        <v>22.8</v>
       </c>
       <c r="K3">
         <v>12.5</v>
@@ -5255,13 +5243,13 @@
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="V3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="W3">
         <v>0.6667</v>
@@ -5351,10 +5339,10 @@
         <v>341.7</v>
       </c>
       <c r="AZ3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB3">
         <v>88.2</v>
@@ -5441,7 +5429,7 @@
         <v>1.1184</v>
       </c>
       <c r="CD3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE3">
         <v>2802</v>
@@ -5524,22 +5512,22 @@
         <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H4" t="s">
         <v>200</v>
       </c>
       <c r="I4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J4">
-        <v>21.7</v>
+        <v>22.8</v>
       </c>
       <c r="K4">
         <v>13.5</v>
@@ -5569,13 +5557,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
+        <v>371</v>
+      </c>
+      <c r="U4" t="s">
+        <v>374</v>
+      </c>
+      <c r="V4" t="s">
         <v>375</v>
-      </c>
-      <c r="U4" t="s">
-        <v>378</v>
-      </c>
-      <c r="V4" t="s">
-        <v>379</v>
       </c>
       <c r="W4">
         <v>0.6667</v>
@@ -5665,10 +5653,10 @@
         <v>340.6</v>
       </c>
       <c r="AZ4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB4">
         <v>87.5</v>
@@ -5755,7 +5743,7 @@
         <v>1.1178</v>
       </c>
       <c r="CD4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE4">
         <v>2835</v>
@@ -5838,22 +5826,22 @@
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H5" t="s">
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J5">
-        <v>21.7</v>
+        <v>22.8</v>
       </c>
       <c r="K5">
         <v>14.5</v>
@@ -5883,13 +5871,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
+        <v>371</v>
+      </c>
+      <c r="U5" t="s">
         <v>375</v>
       </c>
-      <c r="U5" t="s">
-        <v>379</v>
-      </c>
       <c r="V5" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="W5">
         <v>0.6667</v>
@@ -5979,10 +5967,10 @@
         <v>340.9</v>
       </c>
       <c r="AZ5" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA5" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB5">
         <v>88.5</v>
@@ -6069,7 +6057,7 @@
         <v>1.1175</v>
       </c>
       <c r="CD5" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE5">
         <v>2865</v>
@@ -6152,22 +6140,22 @@
         <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F6" t="s">
         <v>110</v>
       </c>
       <c r="G6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H6" t="s">
         <v>201</v>
       </c>
       <c r="I6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J6">
-        <v>140.9</v>
+        <v>142</v>
       </c>
       <c r="K6">
         <v>16.5</v>
@@ -6197,13 +6185,13 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U6" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V6" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W6">
         <v>0.6667</v>
@@ -6293,10 +6281,10 @@
         <v>357.6</v>
       </c>
       <c r="AZ6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB6">
         <v>93.90000000000001</v>
@@ -6383,7 +6371,7 @@
         <v>1.141</v>
       </c>
       <c r="CD6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE6">
         <v>2215</v>
@@ -6466,22 +6454,22 @@
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H7" t="s">
         <v>201</v>
       </c>
       <c r="I7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J7">
-        <v>140.9</v>
+        <v>142</v>
       </c>
       <c r="K7">
         <v>17.5</v>
@@ -6511,13 +6499,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U7" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W7">
         <v>0.6667</v>
@@ -6529,7 +6517,7 @@
         <v>91.8</v>
       </c>
       <c r="Z7">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="AA7">
         <v>0.96</v>
@@ -6607,10 +6595,10 @@
         <v>357.5</v>
       </c>
       <c r="AZ7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB7">
         <v>92.09999999999999</v>
@@ -6697,7 +6685,7 @@
         <v>1.1472</v>
       </c>
       <c r="CD7" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE7">
         <v>2034</v>
@@ -6780,22 +6768,22 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H8" t="s">
         <v>201</v>
       </c>
       <c r="I8" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J8">
-        <v>140.9</v>
+        <v>142</v>
       </c>
       <c r="K8">
         <v>18.5</v>
@@ -6825,13 +6813,13 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V8" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W8">
         <v>0.6667</v>
@@ -6921,10 +6909,10 @@
         <v>359.6</v>
       </c>
       <c r="AZ8" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA8" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB8">
         <v>95.2</v>
@@ -7011,7 +6999,7 @@
         <v>1.1537</v>
       </c>
       <c r="CD8" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE8">
         <v>1842</v>
@@ -7094,22 +7082,22 @@
         <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H9" t="s">
         <v>201</v>
       </c>
       <c r="I9" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J9">
-        <v>140.9</v>
+        <v>142</v>
       </c>
       <c r="K9">
         <v>19.5</v>
@@ -7139,13 +7127,13 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V9" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W9">
         <v>0.6667</v>
@@ -7235,10 +7223,10 @@
         <v>0.1</v>
       </c>
       <c r="AZ9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA9" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB9">
         <v>97.90000000000001</v>
@@ -7325,7 +7313,7 @@
         <v>1.1592</v>
       </c>
       <c r="CD9" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE9">
         <v>1671</v>
@@ -7408,22 +7396,22 @@
         <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F10" t="s">
         <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H10" t="s">
         <v>202</v>
       </c>
       <c r="I10" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J10">
-        <v>144</v>
+        <v>145.1</v>
       </c>
       <c r="K10">
         <v>16.5</v>
@@ -7453,13 +7441,13 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U10" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V10" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W10">
         <v>0.6667</v>
@@ -7549,10 +7537,10 @@
         <v>314.5</v>
       </c>
       <c r="AZ10" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA10" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB10">
         <v>77.7</v>
@@ -7639,7 +7627,7 @@
         <v>1.1255</v>
       </c>
       <c r="CD10" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE10">
         <v>2586</v>
@@ -7722,22 +7710,22 @@
         <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H11" t="s">
         <v>202</v>
       </c>
       <c r="I11" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J11">
-        <v>144</v>
+        <v>145.1</v>
       </c>
       <c r="K11">
         <v>17.5</v>
@@ -7767,13 +7755,13 @@
         <v>56.2</v>
       </c>
       <c r="T11" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U11" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V11" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W11">
         <v>0.6667</v>
@@ -7863,10 +7851,10 @@
         <v>318</v>
       </c>
       <c r="AZ11" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BA11" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BB11">
         <v>27.2</v>
@@ -7953,7 +7941,7 @@
         <v>1.1292</v>
       </c>
       <c r="CD11" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE11">
         <v>2476</v>
@@ -8036,22 +8024,22 @@
         <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H12" t="s">
         <v>202</v>
       </c>
       <c r="I12" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J12">
-        <v>144</v>
+        <v>145.1</v>
       </c>
       <c r="K12">
         <v>18.5</v>
@@ -8081,13 +8069,13 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U12" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V12" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W12">
         <v>0.6667</v>
@@ -8114,7 +8102,7 @@
         <v>0.2</v>
       </c>
       <c r="AE12" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AF12">
         <v>73.59999999999999</v>
@@ -8177,10 +8165,10 @@
         <v>321.1</v>
       </c>
       <c r="AZ12" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA12" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB12">
         <v>89.2</v>
@@ -8267,7 +8255,7 @@
         <v>1.1343</v>
       </c>
       <c r="CD12" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE12">
         <v>2329</v>
@@ -8350,22 +8338,22 @@
         <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G13" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H13" t="s">
         <v>202</v>
       </c>
       <c r="I13" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J13">
-        <v>144</v>
+        <v>145.1</v>
       </c>
       <c r="K13">
         <v>19.5</v>
@@ -8395,13 +8383,13 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U13" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V13" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W13">
         <v>0.6667</v>
@@ -8491,10 +8479,10 @@
         <v>313.9</v>
       </c>
       <c r="AZ13" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA13" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB13">
         <v>95.5</v>
@@ -8581,7 +8569,7 @@
         <v>1.1402</v>
       </c>
       <c r="CD13" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE13">
         <v>2168</v>
@@ -8664,22 +8652,22 @@
         <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F14" t="s">
         <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H14" t="s">
         <v>203</v>
       </c>
       <c r="I14" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J14">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="K14">
         <v>16.5</v>
@@ -8709,13 +8697,13 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U14" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V14" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W14">
         <v>0.6667</v>
@@ -8805,10 +8793,10 @@
         <v>261.3</v>
       </c>
       <c r="AZ14" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA14" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB14">
         <v>95.59999999999999</v>
@@ -8895,7 +8883,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD14" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE14">
         <v>858</v>
@@ -8978,22 +8966,22 @@
         <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F15" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G15" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H15" t="s">
         <v>203</v>
       </c>
       <c r="I15" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J15">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="K15">
         <v>17.5</v>
@@ -9023,13 +9011,13 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V15" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W15">
         <v>0.6667</v>
@@ -9056,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AF15">
         <v>82.40000000000001</v>
@@ -9119,10 +9107,10 @@
         <v>252.6</v>
       </c>
       <c r="AZ15" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA15" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB15">
         <v>97.3</v>
@@ -9209,7 +9197,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD15" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE15">
         <v>858</v>
@@ -9292,22 +9280,22 @@
         <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F16" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G16" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H16" t="s">
         <v>203</v>
       </c>
       <c r="I16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J16">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="K16">
         <v>18.5</v>
@@ -9337,13 +9325,13 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U16" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V16" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W16">
         <v>0.6667</v>
@@ -9433,10 +9421,10 @@
         <v>248.8</v>
       </c>
       <c r="AZ16" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA16" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB16">
         <v>94.40000000000001</v>
@@ -9523,7 +9511,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD16" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE16">
         <v>858</v>
@@ -9606,22 +9594,22 @@
         <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F17" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H17" t="s">
         <v>203</v>
       </c>
       <c r="I17" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J17">
-        <v>53.2</v>
+        <v>54.3</v>
       </c>
       <c r="K17">
         <v>19.5</v>
@@ -9651,13 +9639,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U17" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V17" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W17">
         <v>0.6667</v>
@@ -9747,10 +9735,10 @@
         <v>240.5</v>
       </c>
       <c r="AZ17" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BA17" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BB17">
         <v>82.3</v>
@@ -9837,7 +9825,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE17">
         <v>858</v>
@@ -9920,22 +9908,22 @@
         <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F18" t="s">
         <v>110</v>
       </c>
       <c r="G18" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H18" t="s">
         <v>204</v>
       </c>
       <c r="I18" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J18">
-        <v>578.9</v>
+        <v>580.1</v>
       </c>
       <c r="K18">
         <v>16.5</v>
@@ -9965,13 +9953,13 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U18" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V18" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W18">
         <v>0.6667</v>
@@ -10061,10 +10049,10 @@
         <v>233.9</v>
       </c>
       <c r="AZ18" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BA18" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BB18">
         <v>93.8</v>
@@ -10151,7 +10139,7 @@
         <v>1.1521</v>
       </c>
       <c r="CD18" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE18">
         <v>1764</v>
@@ -10234,22 +10222,22 @@
         <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F19" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H19" t="s">
         <v>204</v>
       </c>
       <c r="I19" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J19">
-        <v>578.9</v>
+        <v>580.1</v>
       </c>
       <c r="K19">
         <v>17.5</v>
@@ -10279,13 +10267,13 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U19" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V19" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W19">
         <v>0.6667</v>
@@ -10375,10 +10363,10 @@
         <v>234.1</v>
       </c>
       <c r="AZ19" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BA19" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BB19">
         <v>93.59999999999999</v>
@@ -10465,7 +10453,7 @@
         <v>1.1545</v>
       </c>
       <c r="CD19" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE19">
         <v>1690</v>
@@ -10548,22 +10536,22 @@
         <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F20" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H20" t="s">
         <v>204</v>
       </c>
       <c r="I20" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J20">
-        <v>578.9</v>
+        <v>580.1</v>
       </c>
       <c r="K20">
         <v>18.5</v>
@@ -10593,13 +10581,13 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U20" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V20" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W20">
         <v>0.6667</v>
@@ -10689,10 +10677,10 @@
         <v>251.9</v>
       </c>
       <c r="AZ20" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BA20" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BB20">
         <v>93</v>
@@ -10779,7 +10767,7 @@
         <v>1.1581</v>
       </c>
       <c r="CD20" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE20">
         <v>1574</v>
@@ -10862,22 +10850,22 @@
         <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F21" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G21" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H21" t="s">
         <v>204</v>
       </c>
       <c r="I21" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J21">
-        <v>578.9</v>
+        <v>580.1</v>
       </c>
       <c r="K21">
         <v>19.5</v>
@@ -10907,13 +10895,13 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U21" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V21" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W21">
         <v>0.6667</v>
@@ -11003,10 +10991,10 @@
         <v>232.5</v>
       </c>
       <c r="AZ21" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BA21" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BB21">
         <v>93.59999999999999</v>
@@ -11093,7 +11081,7 @@
         <v>1.1604</v>
       </c>
       <c r="CD21" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE21">
         <v>1501</v>
@@ -11176,22 +11164,22 @@
         <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F22" t="s">
         <v>111</v>
       </c>
       <c r="G22" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H22" t="s">
         <v>205</v>
       </c>
       <c r="I22" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J22">
-        <v>197.5</v>
+        <v>198.7</v>
       </c>
       <c r="K22">
         <v>16.6</v>
@@ -11221,13 +11209,13 @@
         <v>56.2</v>
       </c>
       <c r="T22" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U22" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V22" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W22">
         <v>0.75</v>
@@ -11317,10 +11305,10 @@
         <v>88.8</v>
       </c>
       <c r="AZ22" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BA22" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BB22">
         <v>16.3</v>
@@ -11407,7 +11395,7 @@
         <v>1.1527</v>
       </c>
       <c r="CD22" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE22">
         <v>1745</v>
@@ -11490,22 +11478,22 @@
         <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F23" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G23" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H23" t="s">
         <v>205</v>
       </c>
       <c r="I23" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J23">
-        <v>197.5</v>
+        <v>198.7</v>
       </c>
       <c r="K23">
         <v>17.6</v>
@@ -11535,13 +11523,13 @@
         <v>56.2</v>
       </c>
       <c r="T23" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U23" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V23" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W23">
         <v>0.75</v>
@@ -11568,7 +11556,7 @@
         <v>0.5</v>
       </c>
       <c r="AE23" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="AF23">
         <v>75.3</v>
@@ -11631,10 +11619,10 @@
         <v>95.90000000000001</v>
       </c>
       <c r="AZ23" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="BA23" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="BB23">
         <v>5</v>
@@ -11721,7 +11709,7 @@
         <v>1.1583</v>
       </c>
       <c r="CD23" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE23">
         <v>1594</v>
@@ -11804,22 +11792,22 @@
         <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F24" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G24" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H24" t="s">
         <v>205</v>
       </c>
       <c r="I24" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J24">
-        <v>197.5</v>
+        <v>198.7</v>
       </c>
       <c r="K24">
         <v>18.6</v>
@@ -11849,13 +11837,13 @@
         <v>56.2</v>
       </c>
       <c r="T24" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U24" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V24" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W24">
         <v>0.75</v>
@@ -11939,16 +11927,16 @@
         <v>11.5</v>
       </c>
       <c r="AX24" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AY24">
         <v>116.1</v>
       </c>
       <c r="AZ24" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="BA24" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="BB24">
         <v>5</v>
@@ -12035,7 +12023,7 @@
         <v>1.1612</v>
       </c>
       <c r="CD24" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE24">
         <v>1510</v>
@@ -12118,22 +12106,22 @@
         <v>124</v>
       </c>
       <c r="E25" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F25" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G25" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H25" t="s">
         <v>205</v>
       </c>
       <c r="I25" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J25">
-        <v>197.5</v>
+        <v>198.7</v>
       </c>
       <c r="K25">
         <v>19.6</v>
@@ -12163,13 +12151,13 @@
         <v>56.2</v>
       </c>
       <c r="T25" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U25" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V25" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W25">
         <v>0.75</v>
@@ -12259,10 +12247,10 @@
         <v>344.1</v>
       </c>
       <c r="AZ25" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BA25" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BB25">
         <v>12.2</v>
@@ -12349,7 +12337,7 @@
         <v>1.1625</v>
       </c>
       <c r="CD25" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE25">
         <v>1470</v>
@@ -12432,22 +12420,22 @@
         <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F26" t="s">
         <v>112</v>
       </c>
       <c r="G26" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I26" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J26">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="K26">
         <v>17</v>
@@ -12477,13 +12465,13 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U26" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V26" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W26">
         <v>0.1667</v>
@@ -12573,10 +12561,10 @@
         <v>351.1</v>
       </c>
       <c r="AZ26" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA26" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB26">
         <v>93.2</v>
@@ -12663,7 +12651,7 @@
         <v>1.126</v>
       </c>
       <c r="CD26" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE26">
         <v>2612</v>
@@ -12746,22 +12734,22 @@
         <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F27" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G27" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I27" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J27">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="K27">
         <v>18</v>
@@ -12791,13 +12779,13 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U27" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V27" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W27">
         <v>0.1667</v>
@@ -12887,10 +12875,10 @@
         <v>349.2</v>
       </c>
       <c r="AZ27" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA27" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB27">
         <v>92.7</v>
@@ -12977,7 +12965,7 @@
         <v>1.1304</v>
       </c>
       <c r="CD27" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE27">
         <v>2478</v>
@@ -13060,22 +13048,22 @@
         <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F28" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G28" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I28" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J28">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="K28">
         <v>19</v>
@@ -13105,13 +13093,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U28" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V28" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W28">
         <v>0.1667</v>
@@ -13201,10 +13189,10 @@
         <v>351</v>
       </c>
       <c r="AZ28" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA28" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB28">
         <v>93.2</v>
@@ -13291,7 +13279,7 @@
         <v>1.1377</v>
       </c>
       <c r="CD28" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE28">
         <v>2250</v>
@@ -13374,22 +13362,22 @@
         <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G29" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I29" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="J29">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="K29">
         <v>20</v>
@@ -13419,13 +13407,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U29" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="V29" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="W29">
         <v>0.1667</v>
@@ -13515,10 +13503,10 @@
         <v>336.5</v>
       </c>
       <c r="AZ29" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA29" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB29">
         <v>89.3</v>
@@ -13605,7 +13593,7 @@
         <v>1.1434</v>
       </c>
       <c r="CD29" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE29">
         <v>2078</v>
@@ -13688,22 +13676,22 @@
         <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F30" t="s">
         <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I30" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J30">
-        <v>679</v>
+        <v>680.1</v>
       </c>
       <c r="K30">
         <v>17</v>
@@ -13733,13 +13721,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U30" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V30" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W30">
         <v>0.1667</v>
@@ -13829,10 +13817,10 @@
         <v>171.7</v>
       </c>
       <c r="AZ30" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA30" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB30">
         <v>92.3</v>
@@ -13919,7 +13907,7 @@
         <v>1.1645</v>
       </c>
       <c r="CD30" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE30">
         <v>1425</v>
@@ -14002,22 +13990,22 @@
         <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F31" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G31" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I31" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J31">
-        <v>679</v>
+        <v>680.1</v>
       </c>
       <c r="K31">
         <v>18</v>
@@ -14047,13 +14035,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U31" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V31" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W31">
         <v>0.1667</v>
@@ -14143,10 +14131,10 @@
         <v>173.3</v>
       </c>
       <c r="AZ31" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA31" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB31">
         <v>95.5</v>
@@ -14233,7 +14221,7 @@
         <v>1.1659</v>
       </c>
       <c r="CD31" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE31">
         <v>1387</v>
@@ -14316,22 +14304,22 @@
         <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F32" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G32" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I32" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J32">
-        <v>679</v>
+        <v>680.1</v>
       </c>
       <c r="K32">
         <v>19</v>
@@ -14361,13 +14349,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U32" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V32" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W32">
         <v>0.1667</v>
@@ -14394,7 +14382,7 @@
         <v>0.1</v>
       </c>
       <c r="AE32" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AF32">
         <v>73.3</v>
@@ -14457,10 +14445,10 @@
         <v>178.4</v>
       </c>
       <c r="AZ32" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA32" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB32">
         <v>93.40000000000001</v>
@@ -14547,7 +14535,7 @@
         <v>1.1679</v>
       </c>
       <c r="CD32" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE32">
         <v>1326</v>
@@ -14630,22 +14618,22 @@
         <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F33" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G33" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="H33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I33" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J33">
-        <v>679</v>
+        <v>680.1</v>
       </c>
       <c r="K33">
         <v>20</v>
@@ -14675,13 +14663,13 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U33" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="V33" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="W33">
         <v>0.1667</v>
@@ -14708,7 +14696,7 @@
         <v>0.1</v>
       </c>
       <c r="AE33" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AF33">
         <v>71.8</v>
@@ -14771,10 +14759,10 @@
         <v>173.9</v>
       </c>
       <c r="AZ33" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA33" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB33">
         <v>92.2</v>
@@ -14861,7 +14849,7 @@
         <v>1.1716</v>
       </c>
       <c r="CD33" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE33">
         <v>1228</v>
@@ -14944,22 +14932,22 @@
         <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F34" t="s">
         <v>113</v>
       </c>
       <c r="G34" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H34" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I34" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J34">
-        <v>34.1</v>
+        <v>35.3</v>
       </c>
       <c r="K34">
         <v>17.5</v>
@@ -14989,13 +14977,13 @@
         <v>18.8</v>
       </c>
       <c r="T34" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U34" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V34" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W34">
         <v>0.6667</v>
@@ -15085,10 +15073,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AZ34" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="BA34" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="BB34">
         <v>49.1</v>
@@ -15175,7 +15163,7 @@
         <v>1.1134</v>
       </c>
       <c r="CD34" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE34">
         <v>3081</v>
@@ -15258,22 +15246,22 @@
         <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F35" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G35" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H35" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I35" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J35">
-        <v>34.1</v>
+        <v>35.3</v>
       </c>
       <c r="K35">
         <v>18.5</v>
@@ -15303,13 +15291,13 @@
         <v>100</v>
       </c>
       <c r="T35" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U35" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V35" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W35">
         <v>0.6667</v>
@@ -15393,16 +15381,16 @@
         <v>7.7</v>
       </c>
       <c r="AX35" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AY35">
         <v>63.1</v>
       </c>
       <c r="AZ35" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BA35" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BB35">
         <v>53.8</v>
@@ -15489,7 +15477,7 @@
         <v>1.1177</v>
       </c>
       <c r="CD35" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE35">
         <v>2943</v>
@@ -15572,22 +15560,22 @@
         <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F36" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G36" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H36" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I36" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J36">
-        <v>34.1</v>
+        <v>35.3</v>
       </c>
       <c r="K36">
         <v>19.5</v>
@@ -15617,13 +15605,13 @@
         <v>100</v>
       </c>
       <c r="T36" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U36" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V36" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W36">
         <v>0.6667</v>
@@ -15713,10 +15701,10 @@
         <v>100.1</v>
       </c>
       <c r="AZ36" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="BA36" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="BB36">
         <v>65.40000000000001</v>
@@ -15803,7 +15791,7 @@
         <v>1.1241</v>
       </c>
       <c r="CD36" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE36">
         <v>2730</v>
@@ -15886,22 +15874,22 @@
         <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F37" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G37" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I37" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J37">
-        <v>34.1</v>
+        <v>35.3</v>
       </c>
       <c r="K37">
         <v>20.5</v>
@@ -15931,13 +15919,13 @@
         <v>100</v>
       </c>
       <c r="T37" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U37" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V37" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W37">
         <v>0.6667</v>
@@ -15964,7 +15952,7 @@
         <v>0.4</v>
       </c>
       <c r="AE37" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AF37">
         <v>81.7</v>
@@ -16021,16 +16009,16 @@
         <v>5</v>
       </c>
       <c r="AX37" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AY37">
         <v>114.7</v>
       </c>
       <c r="AZ37" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="BA37" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="BB37">
         <v>71.40000000000001</v>
@@ -16117,7 +16105,7 @@
         <v>1.1293</v>
       </c>
       <c r="CD37" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE37">
         <v>2559</v>
@@ -16200,22 +16188,22 @@
         <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F38" t="s">
         <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H38" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I38" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="J38">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K38">
         <v>17.5</v>
@@ -16245,13 +16233,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U38" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V38" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W38">
         <v>0.6667</v>
@@ -16341,10 +16329,10 @@
         <v>356.4</v>
       </c>
       <c r="AZ38" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA38" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB38">
         <v>81</v>
@@ -16431,7 +16419,7 @@
         <v>1.1636</v>
       </c>
       <c r="CD38" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE38">
         <v>1536</v>
@@ -16514,22 +16502,22 @@
         <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G39" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H39" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I39" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="J39">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K39">
         <v>18.5</v>
@@ -16559,13 +16547,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U39" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V39" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W39">
         <v>0.6667</v>
@@ -16655,10 +16643,10 @@
         <v>358.1</v>
       </c>
       <c r="AZ39" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA39" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB39">
         <v>82.3</v>
@@ -16745,7 +16733,7 @@
         <v>1.1671</v>
       </c>
       <c r="CD39" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE39">
         <v>1443</v>
@@ -16828,22 +16816,22 @@
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G40" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H40" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I40" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="J40">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K40">
         <v>19.5</v>
@@ -16873,13 +16861,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U40" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V40" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W40">
         <v>0.6667</v>
@@ -16969,10 +16957,10 @@
         <v>0.9</v>
       </c>
       <c r="AZ40" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA40" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB40">
         <v>83.3</v>
@@ -17059,7 +17047,7 @@
         <v>1.1682</v>
       </c>
       <c r="CD40" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE40">
         <v>1411</v>
@@ -17142,22 +17130,22 @@
         <v>127</v>
       </c>
       <c r="E41" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F41" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G41" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I41" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="J41">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K41">
         <v>20.5</v>
@@ -17187,13 +17175,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U41" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V41" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W41">
         <v>0.6667</v>
@@ -17283,10 +17271,10 @@
         <v>4</v>
       </c>
       <c r="AZ41" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA41" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB41">
         <v>85.5</v>
@@ -17373,7 +17361,7 @@
         <v>1.1685</v>
       </c>
       <c r="CD41" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE41">
         <v>1400</v>
@@ -17456,22 +17444,22 @@
         <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F42" t="s">
         <v>114</v>
       </c>
       <c r="G42" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="H42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I42" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J42">
-        <v>79</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K42">
         <v>17.6</v>
@@ -17501,13 +17489,13 @@
         <v>100</v>
       </c>
       <c r="T42" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U42" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V42" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W42">
         <v>0.75</v>
@@ -17597,10 +17585,10 @@
         <v>29.3</v>
       </c>
       <c r="AZ42" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BA42" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BB42">
         <v>94</v>
@@ -17687,7 +17675,7 @@
         <v>1.1229</v>
       </c>
       <c r="CD42" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE42">
         <v>2703</v>
@@ -17770,22 +17758,22 @@
         <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F43" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G43" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="H43" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I43" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J43">
-        <v>79</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K43">
         <v>18.6</v>
@@ -17815,13 +17803,13 @@
         <v>100</v>
       </c>
       <c r="T43" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U43" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V43" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W43">
         <v>0.75</v>
@@ -17911,10 +17899,10 @@
         <v>32.5</v>
       </c>
       <c r="AZ43" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BA43" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BB43">
         <v>94.3</v>
@@ -18001,7 +17989,7 @@
         <v>1.1294</v>
       </c>
       <c r="CD43" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE43">
         <v>2503</v>
@@ -18084,22 +18072,22 @@
         <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F44" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G44" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="H44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I44" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J44">
-        <v>79</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K44">
         <v>19.6</v>
@@ -18129,13 +18117,13 @@
         <v>100</v>
       </c>
       <c r="T44" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U44" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V44" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W44">
         <v>0.75</v>
@@ -18219,16 +18207,16 @@
         <v>8.1</v>
       </c>
       <c r="AX44" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AY44">
         <v>38.5</v>
       </c>
       <c r="AZ44" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BA44" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BB44">
         <v>90.7</v>
@@ -18315,7 +18303,7 @@
         <v>1.1347</v>
       </c>
       <c r="CD44" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE44">
         <v>2327</v>
@@ -18398,22 +18386,22 @@
         <v>128</v>
       </c>
       <c r="E45" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F45" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G45" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="H45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I45" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J45">
-        <v>79</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K45">
         <v>20.6</v>
@@ -18443,13 +18431,13 @@
         <v>100</v>
       </c>
       <c r="T45" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U45" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V45" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W45">
         <v>0.75</v>
@@ -18533,16 +18521,16 @@
         <v>9</v>
       </c>
       <c r="AX45" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AY45">
         <v>44.2</v>
       </c>
       <c r="AZ45" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BA45" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="BB45">
         <v>84.90000000000001</v>
@@ -18629,7 +18617,7 @@
         <v>1.14</v>
       </c>
       <c r="CD45" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE45">
         <v>2165</v>
@@ -18712,25 +18700,25 @@
         <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F46" t="s">
         <v>115</v>
       </c>
       <c r="G46" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H46" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I46" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J46">
-        <v>618.1</v>
+        <v>619.3</v>
       </c>
       <c r="K46">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -18757,13 +18745,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U46" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V46" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W46">
         <v>0.6333</v>
@@ -18853,10 +18841,10 @@
         <v>221.5</v>
       </c>
       <c r="AZ46" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BA46" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BB46">
         <v>93.5</v>
@@ -18943,7 +18931,7 @@
         <v>1.1624</v>
       </c>
       <c r="CD46" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE46">
         <v>1550</v>
@@ -19026,25 +19014,25 @@
         <v>129</v>
       </c>
       <c r="E47" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F47" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G47" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H47" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I47" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J47">
-        <v>618.1</v>
+        <v>619.3</v>
       </c>
       <c r="K47">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="L47">
         <v>5</v>
@@ -19071,13 +19059,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U47" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V47" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W47">
         <v>0.6333</v>
@@ -19086,7 +19074,7 @@
         <v>4.5</v>
       </c>
       <c r="Y47">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="Z47">
         <v>63.8</v>
@@ -19161,16 +19149,16 @@
         <v>4.9</v>
       </c>
       <c r="AX47" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY47">
         <v>204.5</v>
       </c>
       <c r="AZ47" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA47" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB47">
         <v>91.5</v>
@@ -19257,7 +19245,7 @@
         <v>1.1676</v>
       </c>
       <c r="CD47" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE47">
         <v>1389</v>
@@ -19340,25 +19328,25 @@
         <v>129</v>
       </c>
       <c r="E48" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F48" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G48" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I48" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J48">
-        <v>618.1</v>
+        <v>619.3</v>
       </c>
       <c r="K48">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="L48">
         <v>5</v>
@@ -19385,13 +19373,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U48" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V48" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W48">
         <v>0.6333</v>
@@ -19475,16 +19463,16 @@
         <v>4.2</v>
       </c>
       <c r="AX48" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY48">
         <v>196.8</v>
       </c>
       <c r="AZ48" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA48" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB48">
         <v>93.2</v>
@@ -19571,7 +19559,7 @@
         <v>1.1734</v>
       </c>
       <c r="CD48" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE48">
         <v>1212</v>
@@ -19654,25 +19642,25 @@
         <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F49" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G49" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H49" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I49" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J49">
-        <v>618.1</v>
+        <v>619.3</v>
       </c>
       <c r="K49">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -19699,13 +19687,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U49" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V49" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W49">
         <v>0.6333</v>
@@ -19795,10 +19783,10 @@
         <v>188.9</v>
       </c>
       <c r="AZ49" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA49" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB49">
         <v>94.5</v>
@@ -19885,7 +19873,7 @@
         <v>1.1765</v>
       </c>
       <c r="CD49" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE49">
         <v>1114</v>
@@ -19968,22 +19956,22 @@
         <v>130</v>
       </c>
       <c r="E50" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F50" t="s">
         <v>116</v>
       </c>
       <c r="G50" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H50" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I50" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J50">
-        <v>549.7</v>
+        <v>550.8</v>
       </c>
       <c r="K50">
         <v>19.5</v>
@@ -20013,13 +20001,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U50" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V50" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W50">
         <v>0.6667</v>
@@ -20109,10 +20097,10 @@
         <v>223.2</v>
       </c>
       <c r="AZ50" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BA50" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BB50">
         <v>90.2</v>
@@ -20199,7 +20187,7 @@
         <v>1.1382</v>
       </c>
       <c r="CD50" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE50">
         <v>2405</v>
@@ -20282,22 +20270,22 @@
         <v>130</v>
       </c>
       <c r="E51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F51" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G51" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H51" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I51" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J51">
-        <v>549.7</v>
+        <v>550.8</v>
       </c>
       <c r="K51">
         <v>20.5</v>
@@ -20327,13 +20315,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U51" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V51" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W51">
         <v>0.6667</v>
@@ -20417,16 +20405,16 @@
         <v>10.6</v>
       </c>
       <c r="AX51" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY51">
         <v>210.7</v>
       </c>
       <c r="AZ51" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA51" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB51">
         <v>91.09999999999999</v>
@@ -20513,7 +20501,7 @@
         <v>1.1475</v>
       </c>
       <c r="CD51" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE51">
         <v>2105</v>
@@ -20596,22 +20584,22 @@
         <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F52" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G52" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H52" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I52" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J52">
-        <v>549.7</v>
+        <v>550.8</v>
       </c>
       <c r="K52">
         <v>21.5</v>
@@ -20641,13 +20629,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U52" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V52" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W52">
         <v>0.6667</v>
@@ -20731,16 +20719,16 @@
         <v>10.4</v>
       </c>
       <c r="AX52" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY52">
         <v>206.8</v>
       </c>
       <c r="AZ52" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA52" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB52">
         <v>90.90000000000001</v>
@@ -20827,7 +20815,7 @@
         <v>1.1616</v>
       </c>
       <c r="CD52" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE52">
         <v>1673</v>
@@ -20910,22 +20898,22 @@
         <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F53" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G53" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I53" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J53">
-        <v>549.7</v>
+        <v>550.8</v>
       </c>
       <c r="K53">
         <v>22.5</v>
@@ -20955,13 +20943,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U53" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V53" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W53">
         <v>0.6667</v>
@@ -21045,16 +21033,16 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AX53" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY53">
         <v>202.7</v>
       </c>
       <c r="AZ53" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA53" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB53">
         <v>91.5</v>
@@ -21141,7 +21129,7 @@
         <v>1.1712</v>
       </c>
       <c r="CD53" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE53">
         <v>1379</v>
@@ -21224,22 +21212,22 @@
         <v>131</v>
       </c>
       <c r="E54" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F54" t="s">
         <v>116</v>
       </c>
       <c r="G54" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H54" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I54" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J54">
-        <v>618.2</v>
+        <v>619.3</v>
       </c>
       <c r="K54">
         <v>19.5</v>
@@ -21269,13 +21257,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U54" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V54" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W54">
         <v>0.6667</v>
@@ -21365,10 +21353,10 @@
         <v>245.1</v>
       </c>
       <c r="AZ54" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA54" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB54">
         <v>96</v>
@@ -21455,7 +21443,7 @@
         <v>1.1788</v>
       </c>
       <c r="CD54" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE54">
         <v>1057</v>
@@ -21538,22 +21526,22 @@
         <v>131</v>
       </c>
       <c r="E55" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F55" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G55" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H55" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I55" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J55">
-        <v>618.2</v>
+        <v>619.3</v>
       </c>
       <c r="K55">
         <v>20.5</v>
@@ -21583,13 +21571,13 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U55" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V55" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W55">
         <v>0.6667</v>
@@ -21616,7 +21604,7 @@
         <v>-2.4</v>
       </c>
       <c r="AE55" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AF55">
         <v>68.90000000000001</v>
@@ -21679,10 +21667,10 @@
         <v>236</v>
       </c>
       <c r="AZ55" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA55" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB55">
         <v>91.90000000000001</v>
@@ -21769,7 +21757,7 @@
         <v>1.1839</v>
       </c>
       <c r="CD55" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE55">
         <v>906</v>
@@ -21852,22 +21840,22 @@
         <v>131</v>
       </c>
       <c r="E56" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F56" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G56" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H56" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I56" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J56">
-        <v>618.2</v>
+        <v>619.3</v>
       </c>
       <c r="K56">
         <v>21.5</v>
@@ -21897,13 +21885,13 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U56" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V56" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W56">
         <v>0.6667</v>
@@ -21930,7 +21918,7 @@
         <v>-2.4</v>
       </c>
       <c r="AE56" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AF56">
         <v>67.90000000000001</v>
@@ -21993,10 +21981,10 @@
         <v>233.5</v>
       </c>
       <c r="AZ56" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BA56" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BB56">
         <v>75.5</v>
@@ -22083,7 +22071,7 @@
         <v>1.1866</v>
       </c>
       <c r="CD56" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE56">
         <v>828</v>
@@ -22166,22 +22154,22 @@
         <v>131</v>
       </c>
       <c r="E57" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F57" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G57" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H57" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I57" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J57">
-        <v>618.2</v>
+        <v>619.3</v>
       </c>
       <c r="K57">
         <v>22.5</v>
@@ -22211,13 +22199,13 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U57" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V57" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W57">
         <v>0.6667</v>
@@ -22244,7 +22232,7 @@
         <v>-2.4</v>
       </c>
       <c r="AE57" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AF57">
         <v>67.5</v>
@@ -22301,16 +22289,16 @@
         <v>1.4</v>
       </c>
       <c r="AX57" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY57">
         <v>205.7</v>
       </c>
       <c r="AZ57" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA57" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB57">
         <v>70.7</v>
@@ -22397,7 +22385,7 @@
         <v>1.188</v>
       </c>
       <c r="CD57" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE57">
         <v>788</v>
@@ -22480,22 +22468,22 @@
         <v>132</v>
       </c>
       <c r="E58" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F58" t="s">
         <v>117</v>
       </c>
       <c r="G58" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H58" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I58" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J58">
-        <v>163.9</v>
+        <v>165</v>
       </c>
       <c r="K58">
         <v>19.6</v>
@@ -22525,13 +22513,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U58" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="V58" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="W58">
         <v>0.75</v>
@@ -22621,10 +22609,10 @@
         <v>273.6</v>
       </c>
       <c r="AZ58" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BA58" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BB58">
         <v>83</v>
@@ -22711,7 +22699,7 @@
         <v>1.2159</v>
       </c>
       <c r="CD58" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE58">
         <v>68</v>
@@ -22794,22 +22782,22 @@
         <v>132</v>
       </c>
       <c r="E59" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F59" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G59" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H59" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I59" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J59">
-        <v>163.9</v>
+        <v>165</v>
       </c>
       <c r="K59">
         <v>20.6</v>
@@ -22839,13 +22827,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U59" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V59" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W59">
         <v>0.75</v>
@@ -22935,10 +22923,10 @@
         <v>254.1</v>
       </c>
       <c r="AZ59" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BA59" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BB59">
         <v>82.3</v>
@@ -23025,7 +23013,7 @@
         <v>1.2187</v>
       </c>
       <c r="CD59" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE59">
         <v>-13</v>
@@ -23108,22 +23096,22 @@
         <v>132</v>
       </c>
       <c r="E60" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F60" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G60" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H60" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I60" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J60">
-        <v>163.9</v>
+        <v>165</v>
       </c>
       <c r="K60">
         <v>21.6</v>
@@ -23153,13 +23141,13 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U60" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V60" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W60">
         <v>0.75</v>
@@ -23243,16 +23231,16 @@
         <v>11.4</v>
       </c>
       <c r="AX60" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY60">
         <v>211</v>
       </c>
       <c r="AZ60" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BA60" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BB60">
         <v>66.2</v>
@@ -23339,7 +23327,7 @@
         <v>1.2207</v>
       </c>
       <c r="CD60" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="CE60">
         <v>-71</v>
@@ -23422,22 +23410,22 @@
         <v>132</v>
       </c>
       <c r="E61" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F61" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G61" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H61" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I61" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="J61">
-        <v>163.9</v>
+        <v>165</v>
       </c>
       <c r="K61">
         <v>22.6</v>
@@ -23467,13 +23455,13 @@
         <v>56.2</v>
       </c>
       <c r="T61" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U61" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V61" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W61">
         <v>0.75</v>
@@ -23557,16 +23545,16 @@
         <v>9</v>
       </c>
       <c r="AX61" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY61">
         <v>197.2</v>
       </c>
       <c r="AZ61" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BA61" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="BB61">
         <v>61.4</v>
@@ -23653,7 +23641,7 @@
         <v>1.2213</v>
       </c>
       <c r="CD61" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="CE61">
         <v>-90</v>
@@ -23736,22 +23724,22 @@
         <v>133</v>
       </c>
       <c r="E62" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F62" t="s">
         <v>118</v>
       </c>
       <c r="G62" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H62" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I62" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J62">
-        <v>148.8</v>
+        <v>149.8</v>
       </c>
       <c r="K62">
         <v>20</v>
@@ -23781,13 +23769,13 @@
         <v>0</v>
       </c>
       <c r="T62" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U62" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V62" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="W62">
         <v>0.1667</v>
@@ -23877,10 +23865,10 @@
         <v>230.4</v>
       </c>
       <c r="AZ62" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BA62" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="BB62">
         <v>84.5</v>
@@ -23967,7 +23955,7 @@
         <v>1.1447</v>
       </c>
       <c r="CD62" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE62">
         <v>2099</v>
@@ -24050,22 +24038,22 @@
         <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F63" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G63" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H63" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I63" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J63">
-        <v>148.8</v>
+        <v>149.8</v>
       </c>
       <c r="K63">
         <v>21</v>
@@ -24095,13 +24083,13 @@
         <v>0</v>
       </c>
       <c r="T63" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U63" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="V63" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W63">
         <v>0.1667</v>
@@ -24191,10 +24179,10 @@
         <v>215.2</v>
       </c>
       <c r="AZ63" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BA63" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BB63">
         <v>61.3</v>
@@ -24281,7 +24269,7 @@
         <v>1.1522</v>
       </c>
       <c r="CD63" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE63">
         <v>1858</v>
@@ -24364,22 +24352,22 @@
         <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F64" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G64" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H64" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I64" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J64">
-        <v>148.8</v>
+        <v>149.8</v>
       </c>
       <c r="K64">
         <v>22</v>
@@ -24409,13 +24397,13 @@
         <v>18.8</v>
       </c>
       <c r="T64" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U64" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="V64" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="W64">
         <v>0.1667</v>
@@ -24499,16 +24487,16 @@
         <v>2.9</v>
       </c>
       <c r="AX64" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AY64">
         <v>199</v>
       </c>
       <c r="AZ64" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BA64" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="BB64">
         <v>53.1</v>
@@ -24595,7 +24583,7 @@
         <v>1.1567</v>
       </c>
       <c r="CD64" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="CE64">
         <v>1715</v>
@@ -24678,22 +24666,22 @@
         <v>133</v>
       </c>
       <c r="E65" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F65" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G65" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H65" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I65" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J65">
-        <v>148.8</v>
+        <v>149.8</v>
       </c>
       <c r="K65">
         <v>23</v>
@@ -24723,13 +24711,13 @@
         <v>18.8</v>
       </c>
       <c r="T65" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="U65" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="V65" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="W65">
         <v>0.1667</v>
@@ -24819,10 +24807,10 @@
         <v>186.8</v>
       </c>
       <c r="AZ65" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BA65" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="BB65">
         <v>55.1</v>
@@ -24909,7 +24897,7 @@
         <v>1.1608</v>
       </c>
       <c r="CD65" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="CE65">
         <v>1606</v>
